--- a/frontend/public/downloads/template_immobili_control_room.xlsx
+++ b/frontend/public/downloads/template_immobili_control_room.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Immobili" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Istruzioni" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guida compilazione" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valori ammessi" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,13 +44,61 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
       <color rgb="000F172A"/>
-      <sz val="15"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="000066FF"/>
-      <sz val="12"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="0094A3B8"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -65,7 +113,7 @@
       <color rgb="000F172A"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -117,8 +165,28 @@
         <fgColor rgb="000066FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF4FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFBEB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -126,11 +194,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -183,13 +265,68 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1026,349 +1163,1275 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A59"/>
+  <dimension ref="B1:C139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>📘 Istruzioni compilazione template immobili</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="19" t="inlineStr">
+    <row r="1" ht="38" customHeight="1">
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>📘 Guida alla compilazione del template immobili</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>Control Room — Real Estate Portfolio · 38 campi · 8 sezioni · import in massa via Excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>🚀 Come iniziare in 4 step</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • STEP 1 — Cancella la riga di esempio (riga 3) o sovrascrivila con il tuo primo immobile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • STEP 2 — Compila una riga per ogni immobile del tuo portafoglio. Puoi inserire fino a 500 immobili.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • STEP 3 — Salva il file in formato .xlsx (Excel 2007+). Non usare .xls o .csv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • STEP 4 — In Control Room: vai in Centro Import → tab Immobili → trascina il file → controlla l'anteprima → conferma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  💡  Suggerimento: importa prima 1-2 immobili come test, verifica che tutto sia ok, poi carica il resto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>⚙️ Regole generali</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>• Le righe 1 e 2 sono intestazioni: NON modificarle.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>• La riga 3 è un esempio: cancellala o sovrascrivila con i tuoi dati.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>• Inserisci un immobile per riga, a partire dalla riga 3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>• Massimo 500 immobili per file. Per volumi maggiori, divide il file.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>• Salva sempre in formato .xlsx (Excel 2007+).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>✅ Campi obbligatori</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>• Nome immobile — identificatore univoco usato in tutta la piattaforma.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>• Prezzo acquisto — il sistema rifiuta righe senza prezzo o con prezzo ≤ 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>• Tutti gli altri campi sono opzionali ma compilarne di più rende le analisi più precise.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>📅 Formato date</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>• Sempre nel formato YYYY-MM-DD (es. 2024-03-15).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>• Se la data è ignota lascia vuota la cella.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>• Per i contratti di affitto, indicare sia inizio che fine: serve per la timeline e gli alert.</t>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>Struttura del foglio Immobili</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Riga 1: super-header colorato a gruppi (ANAGRAFICA, ACQUISTO, MUTUO…). NON modificare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Riga 2: intestazione colonne. NON modificare né cancellare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Riga 3 in poi: i tuoi dati. Una riga = un immobile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Non lasciare righe vuote in mezzo: se serve, ordina per indirizzo o per data acquisto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>Formato date</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>💶 Formato importi</t>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>Formato richiesto</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD (anno-mese-giorno con trattini)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>• Senza simbolo € e senza separatore migliaia.</t>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>Esempio corretto</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>2024-03-15  oppure  2022-11-08</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>• Usa il punto come separatore decimale (es. 1450.00 o 1450).</t>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>❌ Da evitare</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>15/03/2024 · 15-mar-24 · 03-15-2024 · 2024.03.15</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>• Lascia vuoto se l'importo è 0 o sconosciuto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>🏠 Stato immobile (colonna M)</t>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>Data sconosciuta?</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Lascia la cella vuota. Non scrivere 'NA', 'sconosciuta', '?'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>Formato importi (€)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>• Valori ammessi (dropdown): in_valutazione · in_trattativa · acquistato · in_ristrutturazione · disponibile · affittato · sfitto · in_vendita · venduto.</t>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>Formato richiesto</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>Numero puro, senza € e senza separatore migliaia</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>Esempi corretti</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>1450 · 215000 · 1450.50 · 95000</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>📊 Operazione (colonna N)</t>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>Decimali</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>Usa il PUNTO come separatore (non la virgola): 1450.50, NON 1450,50</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>• reddito → immobile a reddito (affitto).</t>
+      <c r="B29" s="25" t="inlineStr">
+        <is>
+          <t>❌ Da evitare</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>€ 1.450,00 · 1.450€ · 1450,00 · 1450 EUR</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>• compra_vendi → acquisto per rivendita rapida.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>• compra_ristruttura_vendi → acquisto + ristrutturazione + rivendita.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>👤 Inquilino e contratto (colonne X-AC)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>• Email e telefono sono FONDAMENTALI per i solleciti automatici WhatsApp/Email a T+5/15/30 giorni dalla scadenza canone.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>• Telefono in formato internazionale: +393331234567 (no spazi, no trattini).</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>• Email valida (deve contenere @): viene usata anche per generare contratti via PEC futura.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>• Se l'immobile è sfitto/disponibile lascia vuoti tutti i campi inquilino.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>🏦 Mutuo (colonne AE-AK)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>• Compila SOLO se l'immobile è gravato da mutuo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>• Importo originario = quanto la banca ti ha erogato all'inizio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>• Capitale residuo = quanto manca da restituire OGGI (aggiornalo periodicamente).</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>• Tipo tasso (dropdown): fisso · variabile · misto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>• Tutti gli immobili importati con mutuo finiscono automaticamente anche in /mutui per il tracking centralizzato del debito.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="19" t="inlineStr">
-        <is>
-          <t>📐 Dati catastali (colonne K-L)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>• Rendita catastale = valore presente sulla visura catastale (es. 580.50).</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>• Valore catastale = rendita × 168 (immobili residenziali) o × 126 (prima casa). Usato per IMU/scadenzario.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="19" t="inlineStr">
-        <is>
-          <t>🎨 Colori dell'header</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>• Blu scuro = anagrafica · Ciano = dati tecnici · Viola = stato · Verde = acquisto</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>• Teal = valore attuale · Rosso = locazione · Arancio = mutuo · Grigio = note</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="19" t="inlineStr">
-        <is>
-          <t>🚀 Dopo l'import</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>• Vai in Centro Import → Immobili → Trascina il file → Anteprima.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>• Verifica gli avvisi (warnings) sulle righe segnalate prima di confermare.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>• Click su «Conferma import» per creare tutti gli immobili in una volta sola.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>• Gli immobili con dati locazione completi generano automaticamente: contratti, incassi previsti, alert solleciti.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>• Gli immobili con dati mutuo completi generano automaticamente record in /mutui con piano di ammortamento.</t>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>Importo zero?</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>Lascia vuoto, non scrivere 0. Esempio: notaio non sostenuto → vuoto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>Campi obbligatori (segnati con ⚠️ nel resto della guida)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Nome immobile (colonna A) — identificatore univoco usato in tutta la piattaforma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Prezzo acquisto (colonna P) — il sistema rifiuta righe senza prezzo o con prezzo ≤ 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="B35" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ℹ️  Tutti gli altri 36 campi sono opzionali. Più ne compili, più accurate saranno le analisi (rendimento netto, AI Deal Score, alert automatici).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="B37" s="28" t="inlineStr">
+        <is>
+          <t>📋 Dettaglio dei 38 campi (sezione per sezione)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>🔵 ANAGRAFICA (colonne A-H)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="B39" s="29" t="inlineStr">
+        <is>
+          <t>A — Nome immobile ⚠️  ⚠️</t>
+        </is>
+      </c>
+      <c r="C39" s="30" t="inlineStr">
+        <is>
+          <t>Etichetta identificativa univoca. Lo userai in tutta l'app.
+  📝 Esempio: Bilocale Navigli · Trilo Crocetta · Villetta Asti</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="B40" s="31" t="inlineStr">
+        <is>
+          <t>B — Indirizzo</t>
+        </is>
+      </c>
+      <c r="C40" s="30" t="inlineStr">
+        <is>
+          <t>Indirizzo completo con numero civico. Usato per geocoding e mappa.
+  📝 Esempio: Via Vigevano 12 · Corso Vercelli 45/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="B41" s="31" t="inlineStr">
+        <is>
+          <t>C — Città</t>
+        </is>
+      </c>
+      <c r="C41" s="30" t="inlineStr">
+        <is>
+          <t>Comune dell'immobile.
+  📝 Esempio: Milano · Torino · Roma</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="B42" s="31" t="inlineStr">
+        <is>
+          <t>D — Provincia</t>
+        </is>
+      </c>
+      <c r="C42" s="30" t="inlineStr">
+        <is>
+          <t>Sigla provincia (2 lettere maiuscole).
+  📝 Esempio: MI · TO · RM · NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="34" customHeight="1">
+      <c r="B43" s="31" t="inlineStr">
+        <is>
+          <t>E — CAP</t>
+        </is>
+      </c>
+      <c r="C43" s="30" t="inlineStr">
+        <is>
+          <t>5 cifre. Lascialo come testo per preservare gli zeri iniziali.
+  📝 Esempio: 20144 · 10121 · 00184</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="34" customHeight="1">
+      <c r="B44" s="31" t="inlineStr">
+        <is>
+          <t>F — Tipologia</t>
+        </is>
+      </c>
+      <c r="C44" s="30" t="inlineStr">
+        <is>
+          <t>DROPDOWN: Bilocale, Trilocale, Quadrilocale, Monolocale, Villa, Loft, Attico, Negozio, Ufficio, Box, Altro.
+  📝 Esempio: Bilocale</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="B45" s="31" t="inlineStr">
+        <is>
+          <t>G — Metratura (m²)</t>
+        </is>
+      </c>
+      <c r="C45" s="30" t="inlineStr">
+        <is>
+          <t>Superficie commerciale in metri quadrati. Numero intero o decimale.
+  📝 Esempio: 58 · 92.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="34" customHeight="1">
+      <c r="B46" s="31" t="inlineStr">
+        <is>
+          <t>H — Piano</t>
+        </is>
+      </c>
+      <c r="C46" s="30" t="inlineStr">
+        <is>
+          <t>Piano dell'immobile come stringa.
+  📝 Esempio: T (terra) · 1 · 2 · S (seminterrato) · ATT (attico)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t>🩵 DATI TECNICI (colonne I-L)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="34" customHeight="1">
+      <c r="B49" s="31" t="inlineStr">
+        <is>
+          <t>I — Anno costruzione</t>
+        </is>
+      </c>
+      <c r="C49" s="30" t="inlineStr">
+        <is>
+          <t>Anno di costruzione del fabbricato (4 cifre).
+  📝 Esempio: 1972 · 2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="34" customHeight="1">
+      <c r="B50" s="31" t="inlineStr">
+        <is>
+          <t>J — Classe energetica</t>
+        </is>
+      </c>
+      <c r="C50" s="30" t="inlineStr">
+        <is>
+          <t>DROPDOWN: A4, A3, A2, A1, A, B, C, D, E, F, G.
+  📝 Esempio: D · B · A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="34" customHeight="1">
+      <c r="B51" s="31" t="inlineStr">
+        <is>
+          <t>K — Rendita catastale (€)</t>
+        </is>
+      </c>
+      <c r="C51" s="30" t="inlineStr">
+        <is>
+          <t>Valore presente sulla visura catastale.
+  📝 Esempio: 580.50 · 1240</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="34" customHeight="1">
+      <c r="B52" s="31" t="inlineStr">
+        <is>
+          <t>L — Valore catastale (€)</t>
+        </is>
+      </c>
+      <c r="C52" s="30" t="inlineStr">
+        <is>
+          <t>Rendita × 168 (residenziale) o × 126 (prima casa). Usato per IMU e scadenzario fiscale.
+  📝 Esempio: 75000</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="B54" s="24" t="inlineStr">
+        <is>
+          <t>🟣 STATO (colonne M-N)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="42" customHeight="1">
+      <c r="B55" s="31" t="inlineStr">
+        <is>
+          <t>M — Stato</t>
+        </is>
+      </c>
+      <c r="C55" s="30" t="inlineStr">
+        <is>
+          <t>DROPDOWN: in_valutazione, in_trattativa, acquistato, in_ristrutturazione, disponibile, affittato, sfitto, in_vendita, venduto.
+  📝 Esempio: affittato (se locato) · in_vendita (se in vendita)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="34" customHeight="1">
+      <c r="B56" s="31" t="inlineStr">
+        <is>
+          <t>N — Operazione</t>
+        </is>
+      </c>
+      <c r="C56" s="30" t="inlineStr">
+        <is>
+          <t>DROPDOWN: reddito · compra_vendi · compra_ristruttura_vendi.
+  📝 Esempio: reddito (immobile da affittare) · compra_vendi (rivendita)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="B58" s="24" t="inlineStr">
+        <is>
+          <t>🟢 ACQUISTO (colonne O-U)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="34" customHeight="1">
+      <c r="B59" s="31" t="inlineStr">
+        <is>
+          <t>O — Data rogito</t>
+        </is>
+      </c>
+      <c r="C59" s="30" t="inlineStr">
+        <is>
+          <t>Data del rogito notarile.
+  📝 Esempio: 2022-03-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="34" customHeight="1">
+      <c r="B60" s="29" t="inlineStr">
+        <is>
+          <t>P — Prezzo acquisto (€) ⚠️  ⚠️</t>
+        </is>
+      </c>
+      <c r="C60" s="30" t="inlineStr">
+        <is>
+          <t>Prezzo finale al rogito (esclusi notaio/agenzia/imposte). OBBLIGATORIO.
+  📝 Esempio: 215000</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="34" customHeight="1">
+      <c r="B61" s="31" t="inlineStr">
+        <is>
+          <t>Q — Notaio (€)</t>
+        </is>
+      </c>
+      <c r="C61" s="30" t="inlineStr">
+        <is>
+          <t>Costo totale del notaio.
+  📝 Esempio: 4200</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="34" customHeight="1">
+      <c r="B62" s="31" t="inlineStr">
+        <is>
+          <t>R — Agenzia acquisto (€)</t>
+        </is>
+      </c>
+      <c r="C62" s="30" t="inlineStr">
+        <is>
+          <t>Provvigione agenzia (lato acquirente).
+  📝 Esempio: 6500</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="34" customHeight="1">
+      <c r="B63" s="31" t="inlineStr">
+        <is>
+          <t>S — Imposte registro/IVA (€)</t>
+        </is>
+      </c>
+      <c r="C63" s="30" t="inlineStr">
+        <is>
+          <t>Imposta di registro (2% o 9%) o IVA (10% o 22%) a seconda del regime.
+  📝 Esempio: 18500</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="34" customHeight="1">
+      <c r="B64" s="31" t="inlineStr">
+        <is>
+          <t>T — Spese tecniche/perizie (€)</t>
+        </is>
+      </c>
+      <c r="C64" s="30" t="inlineStr">
+        <is>
+          <t>Perizie, visure, geometra, APE alla compravendita.
+  📝 Esempio: 1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="34" customHeight="1">
+      <c r="B65" s="31" t="inlineStr">
+        <is>
+          <t>U — Lavori sostenuti (€)</t>
+        </is>
+      </c>
+      <c r="C65" s="30" t="inlineStr">
+        <is>
+          <t>Costi totali di ristrutturazione/manutenzione sostenuti.
+  📝 Esempio: 18000</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="B67" s="24" t="inlineStr">
+        <is>
+          <t>🩵 VALORE ATTUALE (colonna V)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="34" customHeight="1">
+      <c r="B68" s="31" t="inlineStr">
+        <is>
+          <t>V — Valore stimato attuale (€)</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>Tuo valore di mercato stimato OGGI. Aggiornalo periodicamente. Se vuoto, il sistema usa il prezzo di acquisto.
+  📝 Esempio: 285000</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="B70" s="24" t="inlineStr">
+        <is>
+          <t>🔴 LOCAZIONE (colonne W-AD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="36" customHeight="1">
+      <c r="B71" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ⚠️ IMPORTANTE  Se l'immobile è SFITTO o NON locato, lascia vuote tutte le colonne W-AD. Se è AFFITTATO, compila almeno: canone, inquilino, email/telefono e date contratto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="34" customHeight="1">
+      <c r="B72" s="31" t="inlineStr">
+        <is>
+          <t>W — Canone mensile (€)</t>
+        </is>
+      </c>
+      <c r="C72" s="30" t="inlineStr">
+        <is>
+          <t>Canone netto incassato ogni mese.
+  📝 Esempio: 1450 · 850.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="34" customHeight="1">
+      <c r="B73" s="31" t="inlineStr">
+        <is>
+          <t>X — Inquilino — Nome</t>
+        </is>
+      </c>
+      <c r="C73" s="30" t="inlineStr">
+        <is>
+          <t>Nome completo dell'inquilino.
+  📝 Esempio: Mario Bianchi · Studio Legale Rossi SRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="34" customHeight="1">
+      <c r="B74" s="31" t="inlineStr">
+        <is>
+          <t>Y — Inquilino — Email</t>
+        </is>
+      </c>
+      <c r="C74" s="30" t="inlineStr">
+        <is>
+          <t>🔥 FONDAMENTALE per i solleciti automatici Email a T+5/15/30 giorni dalla scadenza canone.
+  📝 Esempio: mario.bianchi@example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="34" customHeight="1">
+      <c r="B75" s="31" t="inlineStr">
+        <is>
+          <t>Z — Inquilino — Telefono</t>
+        </is>
+      </c>
+      <c r="C75" s="30" t="inlineStr">
+        <is>
+          <t>🔥 FONDAMENTALE per i solleciti automatici WhatsApp. Formato internazionale con prefisso.
+  📝 Esempio: +393331234567 (NO spazi, NO trattini, sì il +)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="34" customHeight="1">
+      <c r="B76" s="31" t="inlineStr">
+        <is>
+          <t>AA — Contratto — Data inizio</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>Data inizio contratto di locazione.
+  📝 Esempio: 2023-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="34" customHeight="1">
+      <c r="B77" s="31" t="inlineStr">
+        <is>
+          <t>AB — Contratto — Data fine</t>
+        </is>
+      </c>
+      <c r="C77" s="30" t="inlineStr">
+        <is>
+          <t>Data fine contratto.
+  📝 Esempio: 2027-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="34" customHeight="1">
+      <c r="B78" s="31" t="inlineStr">
+        <is>
+          <t>AC — Deposito cauzionale (€)</t>
+        </is>
+      </c>
+      <c r="C78" s="30" t="inlineStr">
+        <is>
+          <t>Importo del deposito versato (di solito 3 mensilità).
+  📝 Esempio: 4350</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="34" customHeight="1">
+      <c r="B79" s="31" t="inlineStr">
+        <is>
+          <t>AD — Spese condominiali mensili (€)</t>
+        </is>
+      </c>
+      <c r="C79" s="30" t="inlineStr">
+        <is>
+          <t>Quota mensile spese condominiali a carico tuo (proprietario).
+  📝 Esempio: 95</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="B81" s="24" t="inlineStr">
+        <is>
+          <t>🟠 MUTUO (colonne AE-AK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="36" customHeight="1">
+      <c r="B82" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ℹ️  Compila SOLO se l'immobile è gravato da mutuo. Lascia tutto vuoto altrimenti. Il sistema crea automaticamente un record in /mutui con piano di ammortamento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="34" customHeight="1">
+      <c r="B83" s="31" t="inlineStr">
+        <is>
+          <t>AE — Mutuo — Banca</t>
+        </is>
+      </c>
+      <c r="C83" s="30" t="inlineStr">
+        <is>
+          <t>Banca erogatrice.
+  📝 Esempio: Intesa Sanpaolo · UniCredit · BPER · Crédit Agricole</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="34" customHeight="1">
+      <c r="B84" s="31" t="inlineStr">
+        <is>
+          <t>AF — Mutuo — Importo originario (€)</t>
+        </is>
+      </c>
+      <c r="C84" s="30" t="inlineStr">
+        <is>
+          <t>Capitale inizialmente erogato dalla banca.
+  📝 Esempio: 130000</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="34" customHeight="1">
+      <c r="B85" s="31" t="inlineStr">
+        <is>
+          <t>AG — Mutuo — Capitale residuo (€)</t>
+        </is>
+      </c>
+      <c r="C85" s="30" t="inlineStr">
+        <is>
+          <t>Quanto manca da restituire OGGI. AGGIORNALO periodicamente per LTV accurato.
+  📝 Esempio: 95000</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="34" customHeight="1">
+      <c r="B86" s="31" t="inlineStr">
+        <is>
+          <t>AH — Mutuo — Rata mensile (€)</t>
+        </is>
+      </c>
+      <c r="C86" s="30" t="inlineStr">
+        <is>
+          <t>Rata totale (quota capitale + quota interessi).
+  📝 Esempio: 540</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="34" customHeight="1">
+      <c r="B87" s="31" t="inlineStr">
+        <is>
+          <t>AI — Mutuo — Tasso (%)</t>
+        </is>
+      </c>
+      <c r="C87" s="30" t="inlineStr">
+        <is>
+          <t>Tasso di interesse attuale, come numero (no simbolo %).
+  📝 Esempio: 2.8 · 4.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="34" customHeight="1">
+      <c r="B88" s="31" t="inlineStr">
+        <is>
+          <t>AJ — Mutuo — Tipo tasso</t>
+        </is>
+      </c>
+      <c r="C88" s="30" t="inlineStr">
+        <is>
+          <t>DROPDOWN: fisso · variabile · misto.
+  📝 Esempio: fisso</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="34" customHeight="1">
+      <c r="B89" s="31" t="inlineStr">
+        <is>
+          <t>AK — Mutuo — Data fine</t>
+        </is>
+      </c>
+      <c r="C89" s="30" t="inlineStr">
+        <is>
+          <t>Data prevista di estinzione del mutuo.
+  📝 Esempio: 2042-03-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="22" customHeight="1">
+      <c r="B91" s="24" t="inlineStr">
+        <is>
+          <t>⚪ NOTE (colonna AL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="42" customHeight="1">
+      <c r="B92" s="31" t="inlineStr">
+        <is>
+          <t>AL — Note</t>
+        </is>
+      </c>
+      <c r="C92" s="30" t="inlineStr">
+        <is>
+          <t>Annotazioni libere: caratteristiche peculiari, vincoli, problematiche, opportunità.
+  📝 Esempio: Vista parco · Da rifare bagno · Inquilino in scadenza · Box auto incluso</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="26" customHeight="1">
+      <c r="B94" s="33" t="inlineStr">
+        <is>
+          <t>📚 Esempi pratici di compilazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="22" customHeight="1">
+      <c r="B95" s="24" t="inlineStr">
+        <is>
+          <t>Esempio 1 — Bilocale a reddito con mutuo</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="25" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C96" s="26" t="inlineStr">
+        <is>
+          <t>Immobile acquistato per metterlo a reddito. Affittato a un privato. Mutuo in essere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="25" t="inlineStr">
+        <is>
+          <t>Campi chiave da compilare</t>
+        </is>
+      </c>
+      <c r="C97" s="26" t="inlineStr">
+        <is>
+          <t>Tutti i campi di ANAGRAFICA, ACQUISTO, LOCAZIONE (W-AD), MUTUO (AE-AK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="25" t="inlineStr">
+        <is>
+          <t>Stato</t>
+        </is>
+      </c>
+      <c r="C98" s="26" t="inlineStr">
+        <is>
+          <t>affittato</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="25" t="inlineStr">
+        <is>
+          <t>Operazione</t>
+        </is>
+      </c>
+      <c r="C99" s="26" t="inlineStr">
+        <is>
+          <t>reddito</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="1">
+      <c r="B101" s="24" t="inlineStr">
+        <is>
+          <t>Esempio 2 — Immobile compra-ristruttura-vendi</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="25" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C102" s="26" t="inlineStr">
+        <is>
+          <t>Immobile appena acquistato, in ristrutturazione, da rivendere a fine lavori.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="25" t="inlineStr">
+        <is>
+          <t>Campi chiave da compilare</t>
+        </is>
+      </c>
+      <c r="C103" s="26" t="inlineStr">
+        <is>
+          <t>ANAGRAFICA, ACQUISTO (data, prezzo, costi accessori, lavori), VALORE atteso</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="25" t="inlineStr">
+        <is>
+          <t>Campi da lasciare vuoti</t>
+        </is>
+      </c>
+      <c r="C104" s="26" t="inlineStr">
+        <is>
+          <t>Tutta LOCAZIONE (non sarà affittato), MUTUO (se non finanziato).</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="25" t="inlineStr">
+        <is>
+          <t>Stato</t>
+        </is>
+      </c>
+      <c r="C105" s="26" t="inlineStr">
+        <is>
+          <t>in_ristrutturazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="25" t="inlineStr">
+        <is>
+          <t>Operazione</t>
+        </is>
+      </c>
+      <c r="C106" s="26" t="inlineStr">
+        <is>
+          <t>compra_ristruttura_vendi</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="22" customHeight="1">
+      <c r="B108" s="24" t="inlineStr">
+        <is>
+          <t>Esempio 3 — Immobile a uso personale (no reddito)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="25" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C109" s="26" t="inlineStr">
+        <is>
+          <t>Immobile della società ma non messo a reddito (es. ufficio uso interno).</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="25" t="inlineStr">
+        <is>
+          <t>Stato</t>
+        </is>
+      </c>
+      <c r="C110" s="26" t="inlineStr">
+        <is>
+          <t>disponibile</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="25" t="inlineStr">
+        <is>
+          <t>Operazione</t>
+        </is>
+      </c>
+      <c r="C111" s="26" t="inlineStr">
+        <is>
+          <t>reddito (lascia, anche se canone=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="25" t="inlineStr">
+        <is>
+          <t>Locazione</t>
+        </is>
+      </c>
+      <c r="C112" s="26" t="inlineStr">
+        <is>
+          <t>Lascia tutto vuoto (W-AD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="26" customHeight="1">
+      <c r="B114" s="34" t="inlineStr">
+        <is>
+          <t>❓ FAQ — Domande frequenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="25" t="inlineStr">
+        <is>
+          <t>Q: Posso aggiungere altre colonne al template?</t>
+        </is>
+      </c>
+      <c r="C115" s="26" t="inlineStr">
+        <is>
+          <t>No. Il parser legge SOLO le 38 colonne previste nell'ordine esatto. Colonne aggiuntive vengono ignorate e righe spostate causano errori.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="25" t="inlineStr">
+        <is>
+          <t>Q: Posso riordinare le colonne?</t>
+        </is>
+      </c>
+      <c r="C116" s="26" t="inlineStr">
+        <is>
+          <t>No. L'ordine è fisso. Modifica solo i VALORI dalla riga 3 in poi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="25" t="inlineStr">
+        <is>
+          <t>Q: Cosa succede se sbaglio una data?</t>
+        </is>
+      </c>
+      <c r="C117" s="26" t="inlineStr">
+        <is>
+          <t>Il parser mostra un warning sulla riga e il sistema importa con data vuota. Puoi correggere dopo l'import nella scheda immobile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="25" t="inlineStr">
+        <is>
+          <t>Q: Cosa succede se carico un immobile già esistente?</t>
+        </is>
+      </c>
+      <c r="C118" s="26" t="inlineStr">
+        <is>
+          <t>Il sistema crea sempre un NUOVO record (nessun update automatico). Verifica prima di confermare l'import.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="25" t="inlineStr">
+        <is>
+          <t>Q: I dropdown sono obbligatori?</t>
+        </is>
+      </c>
+      <c r="C119" s="26" t="inlineStr">
+        <is>
+          <t>No, ma usando i valori del dropdown eviti errori di battitura. Se scrivi un valore custom, viene accettato ma il filtraggio per Stato/Operazione potrebbe non funzionare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="25" t="inlineStr">
+        <is>
+          <t>Q: Posso lasciare vuoti i campi mutuo se ho il mutuo?</t>
+        </is>
+      </c>
+      <c r="C120" s="26" t="inlineStr">
+        <is>
+          <t>Sì ma è SCONSIGLIATO. Senza dati mutuo: il cash flow non considera la rata, il debito totale è sottostimato, i KPI di sostenibilità sono sbagliati.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="25" t="inlineStr">
+        <is>
+          <t>Q: Excel mi sta cambiando il CAP 00184 in 184?</t>
+        </is>
+      </c>
+      <c r="C121" s="26" t="inlineStr">
+        <is>
+          <t>Imposta il formato cella della colonna E (CAP) come 'Testo' prima di scrivere. Oppure prefissa con un apostrofo: '00184.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" s="25" t="inlineStr">
+        <is>
+          <t>Q: Errore «Template obsoleto rilevato»?</t>
+        </is>
+      </c>
+      <c r="C122" s="26" t="inlineStr">
+        <is>
+          <t>Hai un vecchio file da 24 colonne. Scarica il nuovo template, ricompila i dati e ricarica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" s="25" t="inlineStr">
+        <is>
+          <t>Q: L'AI estrae automaticamente i dati dal rogito PDF?</t>
+        </is>
+      </c>
+      <c r="C123" s="26" t="inlineStr">
+        <is>
+          <t>Sì, ma solo dopo l'import: vai in Documenti → carica rogito.pdf → click su «AI» → estrazione automatica e aggiornamento della scheda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="26" customHeight="1">
+      <c r="B125" s="20" t="inlineStr">
+        <is>
+          <t>✨ Cosa succede automaticamente dopo l'import</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="30" customHeight="1">
+      <c r="B126" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • 📅 SCADENZARIO: se hai compilato la rendita catastale, vengono generate automaticamente le scadenze IMU (16 giugno acconto, 16 dicembre saldo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="30" customHeight="1">
+      <c r="B127" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • 📨 SOLLECITI: se hai compilato email e telefono dell'inquilino, partono i solleciti automatici T+5/15/30 giorni dalla scadenza canone (WhatsApp + Email pre-compilati).</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="30" customHeight="1">
+      <c r="B128" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • 🏦 MUTUI: se hai compilato banca/residuo/rata, viene creato un record in /mutui con piano di ammortamento e tutti gli alert finanziari (LTV, sostenibilità).</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="30" customHeight="1">
+      <c r="B129" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • 📊 KPI: tutti i KPI di portafoglio (rendimento medio netto, debito totale, cash flow) si aggiornano in tempo reale considerando le tue impostazioni fiscali (SRL/Privato).</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="30" customHeight="1">
+      <c r="B130" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • 🗺️ MAPPA: l'indirizzo viene geocodificato via Nominatim e l'immobile compare sulla mappa colorato in base al rendimento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="30" customHeight="1">
+      <c r="B131" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • 🎯 SCORE: ogni immobile riceve un Portfolio Score 0-100 basato su rendimento, cash flow, rischio, debito.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="30" customHeight="1">
+      <c r="B132" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • 📑 BANKER PACK: gli immobili nuovi entrano automaticamente nel Banker Pack PDF, pronto da presentare in banca.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="26" customHeight="1">
+      <c r="B134" s="35" t="inlineStr">
+        <is>
+          <t>🆘 Hai bisogno di aiuto?</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="18" customHeight="1">
+      <c r="B135" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Consulta il manuale completo nell'app: Sidebar → Manuale → sezione «13. Centro Import».</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="30" customHeight="1">
+      <c r="B136" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Per inserimenti complessi (multi-mutuo per immobile, contratti storici, lavori dettagliati) usa l'interfaccia diretta: Patrimonio → Nuovo immobile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="B137" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Per assistenza all'import in massa di portafogli con 50+ immobili, contatta il supporto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="B139" s="36" t="inlineStr">
+        <is>
+          <t>Real Estate Control Room · Documento generato automaticamente · v2.0 — Template a 38 campi</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="49">
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B134:C134"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B131:C131"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B4:C4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1390,241 +2453,241 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="37" t="inlineStr">
         <is>
           <t>📋 Valori ammessi per campi a dropdown</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="38" t="inlineStr">
         <is>
           <t>Tipologia</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="38" t="inlineStr">
         <is>
           <t>Classe energetica</t>
         </is>
       </c>
-      <c r="C3" s="21" t="inlineStr">
+      <c r="C3" s="38" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
       </c>
-      <c r="D3" s="21" t="inlineStr">
+      <c r="D3" s="38" t="inlineStr">
         <is>
           <t>Operazione</t>
         </is>
       </c>
-      <c r="E3" s="21" t="inlineStr">
+      <c r="E3" s="38" t="inlineStr">
         <is>
           <t>Mutuo — Tipo tasso</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>Bilocale</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="39" t="inlineStr">
         <is>
           <t>in_valutazione</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="39" t="inlineStr">
         <is>
           <t>reddito</t>
         </is>
       </c>
-      <c r="E4" s="22" t="inlineStr">
+      <c r="E4" s="39" t="inlineStr">
         <is>
           <t>fisso</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="39" t="inlineStr">
         <is>
           <t>Trilocale</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="39" t="inlineStr">
         <is>
           <t>in_trattativa</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="39" t="inlineStr">
         <is>
           <t>compra_vendi</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="39" t="inlineStr">
         <is>
           <t>variabile</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="39" t="inlineStr">
         <is>
           <t>Quadrilocale</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="39" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="39" t="inlineStr">
         <is>
           <t>acquistato</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="39" t="inlineStr">
         <is>
           <t>compra_ristruttura_vendi</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="39" t="inlineStr">
         <is>
           <t>misto</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>Monolocale</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="39" t="inlineStr">
         <is>
           <t>in_ristrutturazione</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>Villa</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="39" t="inlineStr">
         <is>
           <t>disponibile</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="39" t="inlineStr">
         <is>
           <t>Loft</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="39" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="39" t="inlineStr">
         <is>
           <t>affittato</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t>Attico</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="39" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="39" t="inlineStr">
         <is>
           <t>sfitto</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="39" t="inlineStr">
         <is>
           <t>Negozio</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="39" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="39" t="inlineStr">
         <is>
           <t>in_vendita</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="39" t="inlineStr">
         <is>
           <t>Ufficio</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="39" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="39" t="inlineStr">
         <is>
           <t>venduto</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="39" t="inlineStr">
         <is>
           <t>Box</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="39" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>Altro</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>G</t>
         </is>
